--- a/output/pdf_financials_xlsx/MARY.xlsx
+++ b/output/pdf_financials_xlsx/MARY.xlsx
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000255</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -872,7 +872,7 @@
         <v>-0.939484</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.232499</v>
+        <v>-0.232754</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.232499</v>
@@ -904,7 +904,7 @@
         <v>-0.939484</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.232499</v>
+        <v>-0.232754</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.232499</v>
@@ -920,7 +920,7 @@
         <v>-1882.205393276435</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1287.441165070048</v>
+        <v>-1288.853203388892</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.044844</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.034632</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.044844</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.034632</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -3881,7 +3881,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>-0.044844</v>
       </c>
@@ -4684,7 +4688,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">

--- a/output/pdf_financials_xlsx/MARY.xlsx
+++ b/output/pdf_financials_xlsx/MARY.xlsx
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.033912</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.033912</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.108535</v>
+        <v>0.07462299999999999</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0.06683500000000001</v>
@@ -1717,10 +1717,8 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.2411159933449938</v>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
@@ -2195,10 +2193,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.002886</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.00072</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -3290,7 +3288,11 @@
           <t>Lease obligations (note 8)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.033912</v>
       </c>
@@ -3540,7 +3542,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.002886</v>
       </c>
